--- a/बजेट माग estimate/JCB log/nagar phiro.xlsx
+++ b/बजेट माग estimate/JCB log/nagar phiro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\JCB log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8D8906-1BA2-4130-9B81-53F207A7BD1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AED19E-418A-4330-8A84-A2BF9390E5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="13" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" firstSheet="13" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="5" r:id="rId1"/>
@@ -90,7 +90,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="24">'25'!$A$1:$H$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="25">'26'!$A$1:$H$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="26">'27'!$A$1:$H$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="27">'28'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'28'!$A$1:$H$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'3'!$A$1:$H$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'4'!$A$1:$H$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'5'!$A$1:$H$34</definedName>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="72">
   <si>
     <t>सुरु घण्टा मिटर (क)</t>
   </si>
@@ -366,12 +366,6 @@
   <si>
     <t xml:space="preserve">सल्लेबाट एसेलु डाँडा काफ्ले सडक </t>
   </si>
-  <si>
-    <t>7/27/2082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">नांग्ले चौकी भन्ज्यांग सडक </t>
-  </si>
 </sst>
 </file>
 
@@ -383,7 +377,7 @@
     <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="167" formatCode="[$-4000439]0.#"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,7 +514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -592,6 +586,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1314,7 +1309,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3BEC72-AA83-4459-9CC2-036ACA69024E}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -1327,7 +1322,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -1339,7 +1334,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -1351,7 +1346,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -1363,7 +1358,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1373,7 +1368,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -1385,7 +1380,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -1397,7 +1392,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -1409,7 +1404,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -1421,7 +1416,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -1447,7 +1442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -1476,7 +1471,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -1491,7 +1486,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -1503,7 +1498,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -1518,7 +1513,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -1533,7 +1528,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -1548,7 +1543,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -1557,7 +1552,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -1568,12 +1563,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -1584,7 +1579,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -1592,11 +1587,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -1605,7 +1600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -1616,7 +1611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -1644,7 +1639,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3730A61-D284-4132-8E16-21F3639E21E6}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -1657,7 +1652,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -1669,7 +1664,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -1681,7 +1676,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -1693,7 +1688,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1703,7 +1698,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -1715,7 +1710,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -1727,7 +1722,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -1739,7 +1734,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -1751,7 +1746,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -1777,7 +1772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -1806,7 +1801,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -1821,7 +1816,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -1833,7 +1828,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -1848,7 +1843,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -1863,7 +1858,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -1878,7 +1873,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -1887,7 +1882,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -1898,12 +1893,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -1914,7 +1909,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -1922,11 +1917,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -1935,7 +1930,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -1946,7 +1941,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -1974,7 +1969,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE02D143-9EFF-4394-87B3-BAF367FB7840}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -1987,7 +1982,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -1999,7 +1994,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -2011,7 +2006,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -2023,7 +2018,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2033,7 +2028,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -2045,7 +2040,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -2057,7 +2052,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -2069,7 +2064,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -2081,7 +2076,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -2107,7 +2102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -2136,7 +2131,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -2163,7 +2158,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -2178,7 +2173,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -2193,7 +2188,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -2208,7 +2203,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -2217,7 +2212,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -2228,12 +2223,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -2244,7 +2239,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -2252,11 +2247,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -2265,7 +2260,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -2276,7 +2271,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -2304,7 +2299,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C636AC1-B13D-4CAE-BDB2-97D1A2954EBF}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -2317,7 +2312,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -2329,7 +2324,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -2341,7 +2336,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -2353,7 +2348,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2363,7 +2358,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -2375,7 +2370,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -2387,7 +2382,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -2399,7 +2394,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -2411,7 +2406,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -2437,7 +2432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -2466,7 +2461,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -2481,7 +2476,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -2493,7 +2488,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -2508,7 +2503,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -2523,7 +2518,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -2538,7 +2533,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -2547,7 +2542,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -2558,12 +2553,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -2574,7 +2569,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -2582,11 +2577,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -2595,7 +2590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -2606,7 +2601,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -2634,7 +2629,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7560295D-302B-4FC1-A733-F0D29A10060E}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -2647,7 +2642,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -2659,7 +2654,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -2671,7 +2666,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -2683,7 +2678,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2693,7 +2688,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -2705,7 +2700,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -2717,7 +2712,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -2729,7 +2724,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -2741,7 +2736,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -2767,7 +2762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -2796,7 +2791,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -2811,7 +2806,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -2823,7 +2818,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -2838,7 +2833,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -2853,7 +2848,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -2868,7 +2863,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -2877,7 +2872,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -2888,12 +2883,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -2904,7 +2899,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -2912,11 +2907,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -2925,7 +2920,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -2936,7 +2931,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -2964,7 +2959,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D6121F-6F22-43E6-9748-1CCED40755B2}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -2977,7 +2972,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -2989,7 +2984,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -3001,7 +2996,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -3013,7 +3008,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3023,7 +3018,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -3035,7 +3030,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -3047,7 +3042,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -3059,7 +3054,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -3071,7 +3066,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -3097,7 +3092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -3126,7 +3121,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -3141,7 +3136,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -3153,7 +3148,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -3168,7 +3163,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -3183,7 +3178,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -3198,7 +3193,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -3207,7 +3202,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -3218,12 +3213,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -3234,7 +3229,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -3242,11 +3237,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -3255,7 +3250,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -3266,7 +3261,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -3294,7 +3289,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AFFAF4A-2A2A-4D83-AC75-67E18BA837B7}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -3307,7 +3302,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -3319,7 +3314,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -3331,7 +3326,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -3343,7 +3338,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3353,7 +3348,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -3365,7 +3360,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -3377,7 +3372,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -3389,7 +3384,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -3401,7 +3396,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -3427,7 +3422,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -3456,7 +3451,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -3471,7 +3466,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -3483,7 +3478,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -3498,7 +3493,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -3513,7 +3508,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -3528,7 +3523,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -3537,7 +3532,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -3548,12 +3543,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -3564,7 +3559,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -3572,11 +3567,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -3585,7 +3580,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -3596,7 +3591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -3624,7 +3619,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB79AFEF-23DA-42ED-BFDA-467B5C781C7D}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -3637,7 +3632,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -3649,7 +3644,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -3661,7 +3656,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -3673,7 +3668,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -3683,7 +3678,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -3695,7 +3690,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -3707,7 +3702,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -3719,7 +3714,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -3731,7 +3726,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -3757,7 +3752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -3786,7 +3781,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -3801,7 +3796,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -3813,7 +3808,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -3828,7 +3823,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -3843,7 +3838,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -3858,7 +3853,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -3867,7 +3862,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -3878,12 +3873,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -3894,7 +3889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -3902,11 +3897,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -3915,7 +3910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -3926,7 +3921,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -3954,7 +3949,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A590A981-C995-4ADA-B741-D59D85CBB520}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -3967,7 +3962,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -3979,7 +3974,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -3991,7 +3986,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -4003,7 +3998,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4013,7 +4008,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -4025,7 +4020,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -4037,7 +4032,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -4049,7 +4044,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -4061,7 +4056,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -4087,7 +4082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -4116,7 +4111,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -4131,7 +4126,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -4143,7 +4138,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -4158,7 +4153,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -4173,7 +4168,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -4188,7 +4183,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -4197,7 +4192,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -4208,12 +4203,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -4224,7 +4219,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -4232,11 +4227,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -4245,7 +4240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -4256,7 +4251,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -4284,7 +4279,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D838B4-0FB5-47BE-9999-9DD1984B8F11}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -4297,7 +4292,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -4309,7 +4304,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -4321,7 +4316,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -4333,7 +4328,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4343,7 +4338,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -4355,7 +4350,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -4367,7 +4362,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -4379,7 +4374,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -4391,7 +4386,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -4417,7 +4412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -4446,7 +4441,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -4461,7 +4456,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -4473,7 +4468,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -4488,7 +4483,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -4503,7 +4498,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -4518,7 +4513,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -4527,7 +4522,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -4538,12 +4533,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -4554,7 +4549,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -4562,11 +4557,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -4575,7 +4570,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -4586,7 +4581,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -4614,7 +4609,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E5971C6-0C98-419E-9BBF-EC6ABCFF9546}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -4627,7 +4622,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -4639,7 +4634,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -4651,7 +4646,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -4663,7 +4658,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4673,7 +4668,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -4685,7 +4680,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -4697,7 +4692,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -4709,7 +4704,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -4721,7 +4716,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -4747,7 +4742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -4776,7 +4771,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -4791,7 +4786,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -4803,7 +4798,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -4818,7 +4813,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -4833,7 +4828,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -4848,7 +4843,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -4857,7 +4852,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -4868,12 +4863,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -4884,7 +4879,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -4892,11 +4887,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -4905,7 +4900,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -4916,7 +4911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -4944,7 +4939,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0AB2CF9-96D6-43D6-885E-0F96BD8DC95E}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -4957,7 +4952,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -4969,7 +4964,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -4981,7 +4976,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -4993,7 +4988,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5003,7 +4998,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -5015,7 +5010,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -5027,7 +5022,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -5039,7 +5034,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -5051,7 +5046,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -5077,7 +5072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -5106,7 +5101,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -5121,7 +5116,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -5133,7 +5128,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -5148,7 +5143,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -5163,7 +5158,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -5178,7 +5173,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -5187,7 +5182,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -5198,12 +5193,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -5214,7 +5209,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -5222,11 +5217,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -5235,7 +5230,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -5246,7 +5241,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -5274,7 +5269,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C874750-C46D-4502-B91B-18265C7074DF}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -5287,7 +5282,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -5299,7 +5294,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -5311,7 +5306,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -5323,7 +5318,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5333,7 +5328,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -5345,7 +5340,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -5357,7 +5352,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -5369,7 +5364,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -5381,7 +5376,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -5407,7 +5402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -5436,7 +5431,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -5451,7 +5446,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -5463,7 +5458,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -5478,7 +5473,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -5493,7 +5488,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -5508,7 +5503,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -5517,7 +5512,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -5528,12 +5523,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -5544,7 +5539,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -5552,11 +5547,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -5565,7 +5560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -5576,7 +5571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -5604,7 +5599,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F870B671-84D9-47D9-81FF-D250938A1125}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -5617,7 +5612,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -5629,7 +5624,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -5641,7 +5636,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -5653,7 +5648,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5663,7 +5658,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -5675,7 +5670,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -5687,7 +5682,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -5699,7 +5694,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -5711,7 +5706,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -5737,7 +5732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -5766,7 +5761,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -5781,7 +5776,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -5793,7 +5788,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -5808,7 +5803,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -5823,7 +5818,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -5838,7 +5833,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -5847,7 +5842,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -5858,12 +5853,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -5874,7 +5869,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -5882,11 +5877,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -5895,7 +5890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -5906,7 +5901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -5934,7 +5929,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D83F9A-26B1-4BDC-B830-A1F686BF653F}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -5947,7 +5942,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -5959,7 +5954,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -5971,7 +5966,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -5983,7 +5978,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5993,7 +5988,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -6005,7 +6000,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -6017,7 +6012,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -6029,7 +6024,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -6041,7 +6036,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -6067,7 +6062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -6096,7 +6091,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -6111,7 +6106,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -6123,7 +6118,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -6138,7 +6133,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -6153,7 +6148,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -6168,7 +6163,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -6177,7 +6172,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -6188,12 +6183,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -6204,7 +6199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -6212,11 +6207,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -6225,7 +6220,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -6236,7 +6231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -6264,7 +6259,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9008835-FB57-42F2-BEC5-D164CD00A9FD}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -6277,7 +6272,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -6289,7 +6284,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -6301,7 +6296,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -6313,7 +6308,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6323,7 +6318,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -6335,7 +6330,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -6347,7 +6342,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -6359,7 +6354,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -6371,7 +6366,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -6397,7 +6392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -6426,7 +6421,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -6441,7 +6436,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -6453,7 +6448,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -6468,7 +6463,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -6483,7 +6478,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -6498,7 +6493,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -6507,7 +6502,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -6518,12 +6513,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -6534,7 +6529,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -6542,11 +6537,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -6555,7 +6550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -6566,7 +6561,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -6594,7 +6589,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7763EF-B248-4C10-940B-A4D94936BBD5}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -6607,7 +6602,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -6619,7 +6614,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -6631,7 +6626,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -6643,7 +6638,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6653,7 +6648,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -6665,7 +6660,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -6677,7 +6672,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -6689,7 +6684,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -6701,7 +6696,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -6727,7 +6722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -6756,7 +6751,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -6771,7 +6766,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -6783,7 +6778,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -6798,7 +6793,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -6813,7 +6808,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -6828,7 +6823,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -6837,7 +6832,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -6848,12 +6843,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -6864,7 +6859,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -6872,11 +6867,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -6885,7 +6880,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -6896,7 +6891,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -6924,7 +6919,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5903EA48-BFBD-4FAD-B217-8B5CF2398BA0}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -6937,7 +6932,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -6949,7 +6944,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -6961,7 +6956,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -6973,7 +6968,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6983,7 +6978,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -6995,7 +6990,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -7007,7 +7002,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -7019,7 +7014,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -7031,7 +7026,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -7057,7 +7052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -7086,7 +7081,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -7101,7 +7096,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -7113,7 +7108,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -7128,7 +7123,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -7143,7 +7138,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -7158,7 +7153,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -7167,7 +7162,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -7178,12 +7173,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -7194,7 +7189,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -7202,11 +7197,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -7215,7 +7210,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -7226,7 +7221,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -7254,7 +7249,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2FDBB1-0210-4F38-9037-7089FBA258D8}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -7267,7 +7262,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -7279,7 +7274,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -7291,7 +7286,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -7303,7 +7298,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7313,7 +7308,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -7325,7 +7320,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -7337,7 +7332,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -7349,7 +7344,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -7361,7 +7356,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -7387,7 +7382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -7416,7 +7411,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -7431,7 +7426,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -7443,7 +7438,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -7458,7 +7453,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -7473,7 +7468,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -7488,7 +7483,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -7497,7 +7492,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -7508,12 +7503,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -7524,7 +7519,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -7532,11 +7527,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -7545,7 +7540,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -7556,7 +7551,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -7584,7 +7579,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8127E0FE-E17F-4664-B9BE-F66F35A858FD}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -7597,7 +7592,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -7609,7 +7604,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -7621,7 +7616,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -7633,7 +7628,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7643,7 +7638,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -7655,7 +7650,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -7667,7 +7662,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -7679,7 +7674,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -7691,7 +7686,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -7717,7 +7712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -7746,7 +7741,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -7761,7 +7756,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -7773,7 +7768,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -7788,7 +7783,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -7803,7 +7798,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -7818,7 +7813,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -7827,7 +7822,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -7838,12 +7833,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -7854,7 +7849,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -7862,11 +7857,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -7875,7 +7870,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -7886,7 +7881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -7913,8 +7908,8 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3D9CC1A-0226-4A13-9D40-ADF9CD88CC3E}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -7927,7 +7922,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -7939,7 +7934,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -7951,7 +7946,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:8" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -7963,7 +7958,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7973,7 +7968,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -7985,7 +7980,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -7997,7 +7992,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -8009,7 +8004,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -8021,7 +8016,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:8" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -8047,184 +8042,209 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
-      <c r="A10" s="6">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="29">
         <v>1</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="18">
-        <v>463</v>
-      </c>
-      <c r="D10" s="19">
-        <v>465.1</v>
-      </c>
-      <c r="E10" s="19">
-        <f t="shared" ref="E10" si="0">D10-C10</f>
-        <v>2.1000000000000227</v>
-      </c>
-      <c r="F10" s="20">
-        <v>2137</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" ref="G10" si="1">F10*E10</f>
-        <v>4487.7000000000489</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="21"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
+        <f t="shared" ref="G10" si="0">F10*E10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="29">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="2">
-        <f>SUM(G10:G10)</f>
-        <v>4487.7000000000489</v>
-      </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="29">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="29">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="2">
-        <f>G11</f>
-        <v>4487.7000000000489</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="29">
+        <v>5</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="2">
-        <f>0.13*G13</f>
-        <v>583.40100000000643</v>
-      </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
       <c r="D15" s="1"/>
       <c r="E15" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="2">
-        <f>SUM(G13:G14)</f>
-        <v>5071.1010000000551</v>
+        <f>SUM(G10:G10)</f>
+        <v>0</v>
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="10"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="23" spans="2:8" ht="20.25">
-      <c r="B23" s="14" t="s">
+    <row r="16" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="2">
+        <f>G15</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="2">
+        <f>0.13*G17</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="2">
+        <f>SUM(G17:G18)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="10"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H26" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
-      <c r="B24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" spans="2:8" ht="18.75">
-      <c r="B25" s="16" t="s">
+    <row r="28" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B28" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E28" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H28" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
-      <c r="C32" s="14" t="s">
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F35" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
-      <c r="C33" s="15"/>
-      <c r="F33" s="15"/>
-    </row>
-    <row r="34" spans="3:6" ht="18.75">
-      <c r="C34" s="16" t="s">
+    <row r="37" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C37" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="F34" s="16" t="s">
+      <c r="D37" s="17"/>
+      <c r="F37" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
-      <c r="C39" s="4" t="s">
+    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
-      <c r="C40" s="4" t="s">
+    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C43" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="4" t="str">
-        <f>E39</f>
+      <c r="E43" s="4" t="str">
+        <f>E42</f>
         <v>without vat</v>
       </c>
     </row>
@@ -8244,7 +8264,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A6AD27-A4B1-40A0-94BE-7AA2F2646239}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -8257,7 +8277,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -8269,7 +8289,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -8281,7 +8301,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -8293,7 +8313,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8303,7 +8323,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -8315,7 +8335,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -8327,7 +8347,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -8339,7 +8359,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -8351,7 +8371,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -8377,7 +8397,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -8406,7 +8426,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -8421,7 +8441,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -8433,7 +8453,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -8448,7 +8468,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -8463,7 +8483,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -8478,7 +8498,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -8487,7 +8507,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -8498,12 +8518,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -8514,7 +8534,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -8522,11 +8542,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -8535,7 +8555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -8546,7 +8566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -8574,7 +8594,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B81F25F-9D86-4821-A4A9-676B99AC283B}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -8587,7 +8607,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -8599,7 +8619,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -8611,7 +8631,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -8623,7 +8643,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8633,7 +8653,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -8645,7 +8665,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -8657,7 +8677,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -8669,7 +8689,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -8681,7 +8701,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -8707,7 +8727,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -8736,7 +8756,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -8751,7 +8771,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -8763,7 +8783,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -8778,7 +8798,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -8793,7 +8813,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -8808,7 +8828,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -8817,7 +8837,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -8828,12 +8848,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -8844,7 +8864,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -8852,11 +8872,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -8865,7 +8885,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -8876,7 +8896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -8904,7 +8924,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03ADCB28-58F1-4430-87F8-ABB8F919B081}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -8917,7 +8937,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -8929,7 +8949,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -8941,7 +8961,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -8953,7 +8973,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8963,7 +8983,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -8975,7 +8995,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -8987,7 +9007,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -8999,7 +9019,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -9011,7 +9031,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -9037,7 +9057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -9066,7 +9086,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -9081,7 +9101,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -9093,7 +9113,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -9108,7 +9128,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -9123,7 +9143,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -9138,7 +9158,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -9147,7 +9167,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -9158,12 +9178,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -9174,7 +9194,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -9182,11 +9202,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -9195,7 +9215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -9206,7 +9226,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -9234,7 +9254,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{826D64F9-E76E-4632-BF9F-EBF31B4ED835}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -9247,7 +9267,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -9259,7 +9279,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -9271,7 +9291,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -9283,7 +9303,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -9293,7 +9313,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -9305,7 +9325,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -9317,7 +9337,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -9329,7 +9349,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -9341,7 +9361,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -9367,7 +9387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -9396,7 +9416,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -9411,7 +9431,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -9423,7 +9443,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -9438,7 +9458,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -9453,7 +9473,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -9468,7 +9488,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -9477,7 +9497,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -9488,12 +9508,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -9504,7 +9524,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -9512,11 +9532,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -9525,7 +9545,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -9536,7 +9556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -9564,7 +9584,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65875523-6736-493C-8964-F373F265DDDC}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -9577,7 +9597,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -9589,7 +9609,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -9601,7 +9621,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -9613,7 +9633,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -9623,7 +9643,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -9635,7 +9655,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -9647,7 +9667,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -9659,7 +9679,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -9671,7 +9691,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -9697,7 +9717,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -9726,7 +9746,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -9741,7 +9761,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -9753,7 +9773,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -9768,7 +9788,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -9783,7 +9803,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -9798,7 +9818,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -9807,7 +9827,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -9818,12 +9838,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -9834,7 +9854,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -9842,11 +9862,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -9855,7 +9875,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -9866,7 +9886,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -9894,7 +9914,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DA8EBA6-A67D-42E1-BAD9-249B1FEFB5FF}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -9907,7 +9927,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -9919,7 +9939,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -9931,7 +9951,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -9943,7 +9963,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -9953,7 +9973,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -9965,7 +9985,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -9977,7 +9997,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -9989,7 +10009,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -10001,7 +10021,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -10027,7 +10047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -10056,7 +10076,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -10071,7 +10091,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -10083,7 +10103,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -10098,7 +10118,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -10113,7 +10133,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -10128,7 +10148,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -10137,7 +10157,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -10148,12 +10168,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -10164,7 +10184,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -10172,11 +10192,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -10185,7 +10205,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -10196,7 +10216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
@@ -10224,7 +10244,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C0144B-CB7A-4392-92BF-119257981438}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" style="4" customWidth="1"/>
@@ -10237,7 +10257,7 @@
     <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50.25" customHeight="1">
+    <row r="1" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="26" t="s">
         <v>4</v>
       </c>
@@ -10249,7 +10269,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="33" customHeight="1">
+    <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
@@ -10261,7 +10281,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" spans="1:10" ht="27">
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
         <v>6</v>
       </c>
@@ -10273,7 +10293,7 @@
       <c r="G3" s="27"/>
       <c r="H3" s="27"/>
     </row>
-    <row r="4" spans="1:10" ht="11.25" customHeight="1">
+    <row r="4" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -10283,7 +10303,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:10" ht="36" customHeight="1">
+    <row r="5" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>16</v>
       </c>
@@ -10295,7 +10315,7 @@
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
+    <row r="6" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="13" t="s">
         <v>26</v>
       </c>
@@ -10307,7 +10327,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
+    <row r="7" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
@@ -10319,7 +10339,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
+    <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
@@ -10331,7 +10351,7 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5">
+    <row r="9" spans="1:10" s="25" customFormat="1" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
         <v>2</v>
       </c>
@@ -10357,7 +10377,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25">
+    <row r="10" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>1</v>
       </c>
@@ -10386,7 +10406,7 @@
       </c>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3"/>
@@ -10401,7 +10421,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -10413,7 +10433,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -10428,7 +10448,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3"/>
@@ -10443,7 +10463,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3"/>
@@ -10458,7 +10478,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
@@ -10467,7 +10487,7 @@
       <c r="G16" s="11"/>
       <c r="H16" s="9"/>
     </row>
-    <row r="23" spans="2:8" ht="20.25">
+    <row r="23" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B23" s="14" t="s">
         <v>15</v>
       </c>
@@ -10478,12 +10498,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="20.25">
+    <row r="24" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B24" s="15"/>
       <c r="E24" s="15"/>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="2:8" ht="18.75">
+    <row r="25" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
         <v>28</v>
       </c>
@@ -10494,7 +10514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="20.25">
+    <row r="32" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C32" s="14" t="s">
         <v>22</v>
       </c>
@@ -10502,11 +10522,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="20.25">
+    <row r="33" spans="3:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C33" s="15"/>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" spans="3:6" ht="18.75">
+    <row r="34" spans="3:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C34" s="16" t="s">
         <v>24</v>
       </c>
@@ -10515,7 +10535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="3:6">
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C39" s="4" t="s">
         <v>17</v>
       </c>
@@ -10526,7 +10546,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C40" s="4" t="s">
         <v>20</v>
       </c>
